--- a/salidas/empresas/EXC.xlsx
+++ b/salidas/empresas/EXC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>18.74025726318359</v>
+        <v>18.74026298522949</v>
       </c>
       <c r="C2" t="n">
         <v>40.95577621459961</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.38827133178711</v>
+        <v>17.38826751708984</v>
       </c>
       <c r="C4" t="n">
         <v>37.7318115234375</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>17.74984169006348</v>
+        <v>17.74984931945801</v>
       </c>
       <c r="C5" t="n">
         <v>38.51640319824219</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.81611824035645</v>
+        <v>18.81611633300781</v>
       </c>
       <c r="C7" t="n">
         <v>40.53495025634766</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.17038345336914</v>
+        <v>19.17039108276367</v>
       </c>
       <c r="C8" t="n">
         <v>41.29814529418945</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.32993316650391</v>
+        <v>20.32993698120117</v>
       </c>
       <c r="C9" t="n">
         <v>43.4950065612793</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.18324089050293</v>
+        <v>20.18324279785156</v>
       </c>
       <c r="C10" t="n">
         <v>43.18117141723633</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.66332054138184</v>
+        <v>20.6633243560791</v>
       </c>
       <c r="C11" t="n">
         <v>44.20827484130859</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.38236045837402</v>
+        <v>20.38236618041992</v>
       </c>
       <c r="C12" t="n">
         <v>43.31668853759766</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.77167510986328</v>
+        <v>20.77167320251465</v>
       </c>
       <c r="C13" t="n">
         <v>44.14408111572266</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.13399505615234</v>
+        <v>20.13400077819824</v>
       </c>
       <c r="C14" t="n">
         <v>42.78887176513672</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.28147125244141</v>
+        <v>22.28147315979004</v>
       </c>
       <c r="C15" t="n">
         <v>47.02567672729492</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.22098731994629</v>
+        <v>23.22099494934082</v>
       </c>
       <c r="C16" t="n">
         <v>49.00856018066406</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>25.48530960083008</v>
+        <v>25.48530578613281</v>
       </c>
       <c r="C17" t="n">
         <v>53.78744888305664</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.51345062255859</v>
+        <v>26.51344108581543</v>
       </c>
       <c r="C18" t="n">
         <v>55.63480758666992</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.67789268493652</v>
+        <v>24.67789840698242</v>
       </c>
       <c r="C19" t="n">
         <v>51.78316879272461</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>23.84510612487793</v>
+        <v>23.84511184692383</v>
       </c>
       <c r="C20" t="n">
         <v>50.03566360473633</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.16783905029297</v>
+        <v>24.1678409576416</v>
       </c>
       <c r="C21" t="n">
         <v>50.40656280517578</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.7717227935791</v>
+        <v>25.77172470092773</v>
       </c>
       <c r="C22" t="n">
         <v>53.75178146362305</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.30921745300293</v>
+        <v>28.30922698974609</v>
       </c>
       <c r="C23" t="n">
         <v>59.04422378540039</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>27.87942695617676</v>
+        <v>27.87942123413086</v>
       </c>
       <c r="C24" t="n">
         <v>57.82453536987305</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.07544326782227</v>
+        <v>28.0754337310791</v>
       </c>
       <c r="C25" t="n">
         <v>58.23109817504883</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>26.17026710510254</v>
+        <v>26.17026519775391</v>
       </c>
       <c r="C26" t="n">
         <v>54.27960205078125</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>25.9030818939209</v>
+        <v>25.90308380126953</v>
       </c>
       <c r="C27" t="n">
         <v>53.38801574707031</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>28.12484169006348</v>
+        <v>28.12485885620117</v>
       </c>
       <c r="C28" t="n">
         <v>57.96718978881836</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>29.58178520202637</v>
+        <v>29.581787109375</v>
       </c>
       <c r="C29" t="n">
         <v>60.97004318237305</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>30.63568115234375</v>
+        <v>30.63567733764648</v>
       </c>
       <c r="C30" t="n">
         <v>62.76747512817383</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>31.31801795959473</v>
+        <v>31.31803894042969</v>
       </c>
       <c r="C31" t="n">
         <v>64.16548156738281</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.37020492553711</v>
+        <v>27.37019920349121</v>
       </c>
       <c r="C32" t="n">
         <v>56.07703399658203</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.62384033203125</v>
+        <v>26.62383842468262</v>
       </c>
       <c r="C33" t="n">
         <v>54.17974472045898</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.94819641113281</v>
+        <v>21.94820213317871</v>
       </c>
       <c r="C34" t="n">
         <v>44.66476440429688</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.01102638244629</v>
+        <v>19.01101493835449</v>
       </c>
       <c r="C35" t="n">
         <v>38.68758773803711</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.6881217956543</v>
+        <v>19.68811988830566</v>
       </c>
       <c r="C37" t="n">
         <v>39.66476440429688</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>16.87594223022461</v>
+        <v>16.87594413757324</v>
       </c>
       <c r="C39" t="n">
         <v>33.68045425415039</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>16.22191429138184</v>
+        <v>16.22192001342773</v>
       </c>
       <c r="C40" t="n">
         <v>32.37517929077148</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.48639106750488</v>
+        <v>16.48638725280762</v>
       </c>
       <c r="C41" t="n">
         <v>32.90299606323242</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>17.336181640625</v>
+        <v>17.3361873626709</v>
       </c>
       <c r="C42" t="n">
         <v>34.24393844604492</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.49168395996094</v>
+        <v>18.4916820526123</v>
       </c>
       <c r="C43" t="n">
         <v>36.52639007568359</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.36530303955078</v>
+        <v>18.36530494689941</v>
       </c>
       <c r="C44" t="n">
         <v>36.27674865722656</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.2520751953125</v>
+        <v>18.25207901000977</v>
       </c>
       <c r="C45" t="n">
         <v>35.67760467529297</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.10611534118652</v>
+        <v>18.10611724853516</v>
       </c>
       <c r="C46" t="n">
         <v>35.39229583740234</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>17.13549423217773</v>
+        <v>17.1354923248291</v>
       </c>
       <c r="C47" t="n">
         <v>33.4950065612793</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.77705955505371</v>
+        <v>17.77706527709961</v>
       </c>
       <c r="C48" t="n">
         <v>34.36519241333008</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>18.03165626525879</v>
+        <v>18.03166198730469</v>
       </c>
       <c r="C49" t="n">
         <v>34.85734558105469</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.83250045776367</v>
+        <v>16.83249855041504</v>
       </c>
       <c r="C50" t="n">
         <v>32.53923034667969</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.16808891296387</v>
+        <v>16.1680965423584</v>
       </c>
       <c r="C51" t="n">
         <v>30.88445091247559</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.35852241516113</v>
+        <v>16.35852813720703</v>
       </c>
       <c r="C52" t="n">
         <v>31.24821662902832</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.2763729095459</v>
+        <v>16.27638244628906</v>
       </c>
       <c r="C53" t="n">
         <v>31.0912971496582</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.59262847900391</v>
+        <v>14.59262371063232</v>
       </c>
       <c r="C54" t="n">
         <v>27.53209686279297</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.35445499420166</v>
+        <v>14.35445404052734</v>
       </c>
       <c r="C55" t="n">
         <v>27.08273887634277</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.81372261047363</v>
+        <v>15.81371402740479</v>
       </c>
       <c r="C56" t="n">
         <v>29.8359489440918</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>15.58900165557861</v>
+        <v>15.5889949798584</v>
       </c>
       <c r="C57" t="n">
         <v>29.04422378540039</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.30107116699219</v>
+        <v>16.30106353759766</v>
       </c>
       <c r="C58" t="n">
         <v>30.37089920043945</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.62727546691895</v>
+        <v>15.62727737426758</v>
       </c>
       <c r="C59" t="n">
         <v>29.11554908752441</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>15.26504516601562</v>
+        <v>15.26505279541016</v>
       </c>
       <c r="C60" t="n">
         <v>28.08131217956543</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>16.14520072937012</v>
+        <v>16.14520263671875</v>
       </c>
       <c r="C61" t="n">
         <v>29.7004280090332</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.48253440856934</v>
+        <v>16.4825267791748</v>
       </c>
       <c r="C62" t="n">
         <v>30.32097053527832</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>16.39060211181641</v>
+        <v>16.39059638977051</v>
       </c>
       <c r="C63" t="n">
         <v>29.78602027893066</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.18650054931641</v>
+        <v>16.18649673461914</v>
       </c>
       <c r="C64" t="n">
         <v>29.41512107849121</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>16.55152130126953</v>
+        <v>16.55152320861816</v>
       </c>
       <c r="C65" t="n">
         <v>30.07845878601074</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.63339614868164</v>
+        <v>16.63339424133301</v>
       </c>
       <c r="C66" t="n">
         <v>29.8502140045166</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.0268726348877</v>
+        <v>17.02687072753906</v>
       </c>
       <c r="C67" t="n">
         <v>30.55634880065918</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>17.51574325561523</v>
+        <v>17.51574516296387</v>
       </c>
       <c r="C68" t="n">
         <v>31.43366622924805</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.36420059204102</v>
+        <v>17.36420249938965</v>
       </c>
       <c r="C69" t="n">
         <v>30.75606346130371</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>17.1588306427002</v>
+        <v>17.15882873535156</v>
       </c>
       <c r="C70" t="n">
         <v>30.39229774475098</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>17.87562370300293</v>
+        <v>17.8756217956543</v>
       </c>
       <c r="C71" t="n">
         <v>31.66191291809082</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.05413627624512</v>
+        <v>18.05413246154785</v>
       </c>
       <c r="C72" t="n">
         <v>31.60485076904297</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.67113304138184</v>
+        <v>17.6711311340332</v>
       </c>
       <c r="C73" t="n">
         <v>30.93437957763672</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>16.2083854675293</v>
+        <v>16.20838356018066</v>
       </c>
       <c r="C74" t="n">
         <v>28.37375259399414</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.13166809082031</v>
+        <v>16.13167190551758</v>
       </c>
       <c r="C75" t="n">
         <v>27.86733245849609</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.24907112121582</v>
+        <v>16.24906730651855</v>
       </c>
       <c r="C76" t="n">
         <v>27.96718978881836</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>16.16618728637695</v>
+        <v>16.16617965698242</v>
       </c>
       <c r="C77" t="n">
         <v>27.82453536987305</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>15.47555255889893</v>
+        <v>15.47555160522461</v>
       </c>
       <c r="C78" t="n">
         <v>26.3766040802002</v>
@@ -2219,7 +2231,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.37110900878906</v>
+        <v>16.37111282348633</v>
       </c>
       <c r="C80" t="n">
         <v>27.90299606323242</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>15.47081851959229</v>
+        <v>15.47081565856934</v>
       </c>
       <c r="C81" t="n">
         <v>26.01283836364746</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>15.09327411651611</v>
+        <v>15.0932731628418</v>
       </c>
       <c r="C82" t="n">
         <v>25.37803077697754</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.17811298370361</v>
+        <v>15.17811012268066</v>
       </c>
       <c r="C83" t="n">
         <v>25.52068519592285</v>
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>12.83489799499512</v>
+        <v>12.83489322662354</v>
       </c>
       <c r="C85" t="n">
         <v>21.21255302429199</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.56856346130371</v>
+        <v>13.56856250762939</v>
       </c>
       <c r="C86" t="n">
         <v>22.42510604858398</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.6003885269165</v>
+        <v>13.60038089752197</v>
       </c>
       <c r="C87" t="n">
         <v>22.1041374206543</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.13202095031738</v>
+        <v>15.13202381134033</v>
       </c>
       <c r="C88" t="n">
         <v>24.59343719482422</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>16.46177291870117</v>
+        <v>16.4617805480957</v>
       </c>
       <c r="C89" t="n">
         <v>26.75463676452637</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.87430000305176</v>
+        <v>13.87429332733154</v>
       </c>
       <c r="C90" t="n">
         <v>22.35378074645996</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>13.67065238952637</v>
+        <v>13.67065143585205</v>
       </c>
       <c r="C91" t="n">
         <v>22.02567863464355</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.54226875305176</v>
+        <v>13.54226970672607</v>
       </c>
       <c r="C92" t="n">
         <v>21.8188304901123</v>
@@ -2625,7 +2637,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>13.25399017333984</v>
+        <v>13.25398540496826</v>
       </c>
       <c r="C94" t="n">
         <v>21.14122772216797</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>12.76210403442383</v>
+        <v>12.7621021270752</v>
       </c>
       <c r="C95" t="n">
         <v>20.35663223266602</v>
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>12.38414764404297</v>
+        <v>12.38414192199707</v>
       </c>
       <c r="C97" t="n">
         <v>19.536376953125</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>13.11209201812744</v>
+        <v>13.11209392547607</v>
       </c>
       <c r="C98" t="n">
         <v>20.68473625183105</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>13.89578342437744</v>
+        <v>13.89577865600586</v>
       </c>
       <c r="C99" t="n">
         <v>21.6904411315918</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.33517360687256</v>
+        <v>15.33517074584961</v>
       </c>
       <c r="C100" t="n">
         <v>23.93723297119141</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>16.00688552856445</v>
+        <v>16.00687980651855</v>
       </c>
       <c r="C101" t="n">
         <v>24.9857349395752</v>
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.81576156616211</v>
+        <v>16.81576728820801</v>
       </c>
       <c r="C103" t="n">
         <v>26.01997184753418</v>
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>15.86842155456543</v>
+        <v>15.86843204498291</v>
       </c>
       <c r="C106" t="n">
         <v>24.31526374816895</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>17.03214263916016</v>
+        <v>17.03214073181152</v>
       </c>
       <c r="C107" t="n">
         <v>26.09843063354492</v>
@@ -3060,7 +3072,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>17.40391159057617</v>
+        <v>17.4039134979248</v>
       </c>
       <c r="C109" t="n">
         <v>26.44793128967285</v>
@@ -3118,7 +3130,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>16.06300354003906</v>
+        <v>16.06299591064453</v>
       </c>
       <c r="C111" t="n">
         <v>24.19400978088379</v>
@@ -3176,7 +3188,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3205,7 +3217,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>16.16934394836426</v>
+        <v>16.16933822631836</v>
       </c>
       <c r="C114" t="n">
         <v>24.12981414794922</v>
@@ -3263,7 +3275,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>15.33768844604492</v>
+        <v>15.33769226074219</v>
       </c>
       <c r="C116" t="n">
         <v>22.88872909545898</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>14.84541702270508</v>
+        <v>14.84542274475098</v>
       </c>
       <c r="C117" t="n">
         <v>21.94008636474609</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>14.33384323120117</v>
+        <v>14.33384418487549</v>
       </c>
       <c r="C118" t="n">
         <v>21.18402290344238</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>13.47477436065674</v>
+        <v>13.47477912902832</v>
       </c>
       <c r="C119" t="n">
         <v>19.91440773010254</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>13.32374668121338</v>
+        <v>13.32374382019043</v>
       </c>
       <c r="C120" t="n">
         <v>19.47931480407715</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.54816627502441</v>
+        <v>13.54816341400146</v>
       </c>
       <c r="C121" t="n">
         <v>19.80741882324219</v>
@@ -3466,7 +3478,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>15.51361465454102</v>
+        <v>15.51361560821533</v>
       </c>
       <c r="C123" t="n">
         <v>22.46076965332031</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>17.66650009155273</v>
+        <v>17.66650390625</v>
       </c>
       <c r="C124" t="n">
         <v>25.57774543762207</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>17.28716278076172</v>
+        <v>17.28716087341309</v>
       </c>
       <c r="C125" t="n">
         <v>25.02853012084961</v>
@@ -3582,7 +3594,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>18.07612991333008</v>
+        <v>18.07613182067871</v>
       </c>
       <c r="C127" t="n">
         <v>25.93437957763672</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>18.53350639343262</v>
+        <v>18.53349685668945</v>
       </c>
       <c r="C128" t="n">
         <v>26.59058570861816</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>17.05551719665527</v>
+        <v>17.05552101135254</v>
       </c>
       <c r="C129" t="n">
         <v>24.25107002258301</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>16.69936561584473</v>
+        <v>16.6993579864502</v>
       </c>
       <c r="C130" t="n">
         <v>23.74464988708496</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>17.09063911437988</v>
+        <v>17.09064102172852</v>
       </c>
       <c r="C131" t="n">
         <v>24.30099868774414</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>16.47141456604004</v>
+        <v>16.47141647338867</v>
       </c>
       <c r="C132" t="n">
         <v>23.18830108642578</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>17.98125839233398</v>
+        <v>17.98125267028809</v>
       </c>
       <c r="C133" t="n">
         <v>25.3138370513916</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>18.17885208129883</v>
+        <v>18.17884826660156</v>
       </c>
       <c r="C134" t="n">
         <v>25.59201049804688</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>18.77522659301758</v>
+        <v>18.77521896362305</v>
       </c>
       <c r="C135" t="n">
         <v>26.18402290344238</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>18.4018726348877</v>
+        <v>18.40187644958496</v>
       </c>
       <c r="C136" t="n">
         <v>25.66333770751953</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7114143371582</v>
+        <v>17.71141242980957</v>
       </c>
       <c r="C137" t="n">
         <v>24.7004280090332</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>18.75284576416016</v>
+        <v>18.75284767150879</v>
       </c>
       <c r="C138" t="n">
         <v>25.89871597290039</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>18.6288948059082</v>
+        <v>18.62889099121094</v>
       </c>
       <c r="C139" t="n">
         <v>25.72753143310547</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>19.80126571655273</v>
+        <v>19.80126190185547</v>
       </c>
       <c r="C140" t="n">
         <v>27.34664726257324</v>
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4046,7 +4058,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>20.94912147521973</v>
+        <v>20.94912338256836</v>
       </c>
       <c r="C143" t="n">
         <v>28.68045616149902</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>21.90128517150879</v>
+        <v>21.90128898620605</v>
       </c>
       <c r="C144" t="n">
         <v>29.75035667419434</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>20.6935920715332</v>
+        <v>20.69359588623047</v>
       </c>
       <c r="C145" t="n">
         <v>28.10984230041504</v>
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>19.63214683532715</v>
+        <v>19.63215255737305</v>
       </c>
       <c r="C147" t="n">
         <v>26.41940116882324</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>20.67629814147949</v>
+        <v>20.67630004882812</v>
       </c>
       <c r="C148" t="n">
         <v>27.82453536987305</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>21.03141593933105</v>
+        <v>21.03141212463379</v>
       </c>
       <c r="C149" t="n">
         <v>28.30242538452148</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>22.12558555603027</v>
+        <v>22.12558937072754</v>
       </c>
       <c r="C150" t="n">
         <v>29.5221118927002</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>22.77241134643555</v>
+        <v>22.77241325378418</v>
       </c>
       <c r="C151" t="n">
         <v>30.38516426086426</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>22.71895217895508</v>
+        <v>22.71895790100098</v>
       </c>
       <c r="C152" t="n">
         <v>30.3138370513916</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>23.55340003967285</v>
+        <v>23.55339241027832</v>
       </c>
       <c r="C153" t="n">
         <v>31.17688941955566</v>
@@ -4394,7 +4406,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>23.6072883605957</v>
+        <v>23.60727882385254</v>
       </c>
       <c r="C155" t="n">
         <v>31.24821662902832</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>25.18680381774902</v>
+        <v>25.18680191040039</v>
       </c>
       <c r="C156" t="n">
         <v>33.08844375610352</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>24.48641586303711</v>
+        <v>24.48641777038574</v>
       </c>
       <c r="C157" t="n">
         <v>32.16833114624023</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>25.93062782287598</v>
+        <v>25.93062210083008</v>
       </c>
       <c r="C158" t="n">
         <v>34.06562042236328</v>
@@ -4539,7 +4551,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>27.42365837097168</v>
+        <v>27.42365264892578</v>
       </c>
       <c r="C160" t="n">
         <v>35.75606155395508</v>
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>26.49525451660156</v>
+        <v>26.49525260925293</v>
       </c>
       <c r="C162" t="n">
         <v>34.29386520385742</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>26.41810417175293</v>
+        <v>26.41810607910156</v>
       </c>
       <c r="C163" t="n">
         <v>34.19400787353516</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>24.8310375213623</v>
+        <v>24.83103179931641</v>
       </c>
       <c r="C164" t="n">
         <v>32.13980102539062</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>26.25273704528809</v>
+        <v>26.25273513793945</v>
       </c>
       <c r="C165" t="n">
         <v>33.70898818969727</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>26.83600616455078</v>
+        <v>26.83600044250488</v>
       </c>
       <c r="C166" t="n">
         <v>34.45791625976562</v>
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,7 +4841,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>26.65347099304199</v>
+        <v>26.65346908569336</v>
       </c>
       <c r="C170" t="n">
         <v>33.94436645507812</v>
@@ -4887,7 +4899,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>20.77389526367188</v>
+        <v>20.77390098571777</v>
       </c>
       <c r="C172" t="n">
         <v>26.25535011291504</v>
@@ -4945,7 +4957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>21.85503387451172</v>
+        <v>21.85503005981445</v>
       </c>
       <c r="C174" t="n">
         <v>27.32525062561035</v>
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>22.02617645263672</v>
+        <v>22.02617454528809</v>
       </c>
       <c r="C176" t="n">
         <v>27.53923034667969</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>21.26677894592285</v>
+        <v>21.26677513122559</v>
       </c>
       <c r="C177" t="n">
         <v>26.32667541503906</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>20.60416984558105</v>
+        <v>20.60416412353516</v>
       </c>
       <c r="C178" t="n">
         <v>25.50641822814941</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>23.87785720825195</v>
+        <v>23.87785530090332</v>
       </c>
       <c r="C180" t="n">
         <v>29.29386520385742</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>24.54645919799805</v>
+        <v>24.54646110534668</v>
       </c>
       <c r="C181" t="n">
         <v>30.11412239074707</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>24.16274070739746</v>
+        <v>24.16273498535156</v>
       </c>
       <c r="C182" t="n">
         <v>29.64336776733398</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>22.44181060791016</v>
+        <v>22.44181251525879</v>
       </c>
       <c r="C183" t="n">
         <v>27.53209686279297</v>
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>26.38191795349121</v>
+        <v>26.38192176818848</v>
       </c>
       <c r="C185" t="n">
         <v>32.05420684814453</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>26.72501564025879</v>
+        <v>26.72501754760742</v>
       </c>
       <c r="C186" t="n">
         <v>32.18259429931641</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>26.24524879455566</v>
+        <v>26.2452507019043</v>
       </c>
       <c r="C187" t="n">
         <v>31.60485076904297</v>
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>27.72009658813477</v>
+        <v>27.7200984954834</v>
       </c>
       <c r="C188" t="n">
         <v>33.38088226318359</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>29.26759147644043</v>
+        <v>29.2675838470459</v>
       </c>
       <c r="C189" t="n">
         <v>34.96433639526367</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>28.86159896850586</v>
+        <v>28.86159515380859</v>
       </c>
       <c r="C190" t="n">
         <v>34.47931671142578</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.7573127746582</v>
+        <v>31.75731086730957</v>
       </c>
       <c r="C191" t="n">
         <v>37.93865966796875</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>31.70465087890625</v>
+        <v>31.70464706420898</v>
       </c>
       <c r="C192" t="n">
         <v>37.61055755615234</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>34.7290153503418</v>
+        <v>34.72901153564453</v>
       </c>
       <c r="C193" t="n">
         <v>41.19828796386719</v>
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5583,7 +5595,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,7 +5682,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.79666900634766</v>
+        <v>38.79666519165039</v>
       </c>
       <c r="C199" t="n">
         <v>45.31999969482422</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>39.79825973510742</v>
+        <v>39.79825592041016</v>
       </c>
       <c r="C200" t="n">
         <v>46.4900016784668</v>
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,7 +5798,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>33.28152465820312</v>
+        <v>33.28153610229492</v>
       </c>
       <c r="C203" t="n">
         <v>38.59000015258789</v>
@@ -5844,7 +5856,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>37.60827255249023</v>
+        <v>37.60826873779297</v>
       </c>
       <c r="C205" t="n">
         <v>43.22999954223633</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>36.70351028442383</v>
+        <v>36.70351409912109</v>
       </c>
       <c r="C206" t="n">
         <v>42.18999862670898</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>35.44254684448242</v>
+        <v>35.44255065917969</v>
       </c>
       <c r="C207" t="n">
         <v>40.38999938964844</v>
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>37.24143600463867</v>
+        <v>37.24143218994141</v>
       </c>
       <c r="C209" t="n">
         <v>42.43999862670898</v>
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>35.09057998657227</v>
+        <v>35.090576171875</v>
       </c>
       <c r="C210" t="n">
         <v>39.65000152587891</v>
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>36.05522537231445</v>
+        <v>36.05522918701172</v>
       </c>
       <c r="C211" t="n">
         <v>40.7400016784668</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>37.04644012451172</v>
+        <v>37.04643249511719</v>
       </c>
       <c r="C212" t="n">
         <v>41.86000061035156</v>
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6134,7 +6146,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>34.77120971679688</v>
+        <v>34.77121734619141</v>
       </c>
       <c r="C215" t="n">
         <v>38.93999862670898</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>34.70929336547852</v>
+        <v>34.70928955078125</v>
       </c>
       <c r="C216" t="n">
         <v>38.5099983215332</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>32.35688781738281</v>
+        <v>32.35689163208008</v>
       </c>
       <c r="C217" t="n">
         <v>35.90000152587891</v>
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>32.30280685424805</v>
+        <v>32.30281066894531</v>
       </c>
       <c r="C219" t="n">
         <v>35.84000015258789</v>
@@ -6308,7 +6320,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,11 +6378,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>34.54924392700195</v>
+        <v>34.54924011230469</v>
       </c>
       <c r="C222" t="n">
         <v>37.54999923706055</v>
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>34.22721481323242</v>
+        <v>34.22721099853516</v>
       </c>
       <c r="C224" t="n">
         <v>37.20000076293945</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>35.40504837036133</v>
+        <v>35.40505218505859</v>
       </c>
       <c r="C225" t="n">
         <v>38.09000015258789</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.691650390625</v>
+        <v>37.69164657592773</v>
       </c>
       <c r="C226" t="n">
         <v>40.54999923706055</v>
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>36.52976226806641</v>
+        <v>36.52975845336914</v>
       </c>
       <c r="C227" t="n">
         <v>39.29999923706055</v>
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>37.14197540283203</v>
+        <v>37.1419792175293</v>
       </c>
       <c r="C228" t="n">
         <v>39.56000137329102</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>35.33932876586914</v>
+        <v>35.33933258056641</v>
       </c>
       <c r="C229" t="n">
         <v>37.63999938964844</v>
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,11 +6639,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>41.88447952270508</v>
+        <v>41.88448715209961</v>
       </c>
       <c r="C231" t="n">
         <v>44.20000076293945</v>
@@ -6656,7 +6668,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>41.89505767822266</v>
+        <v>41.89506149291992</v>
       </c>
       <c r="C234" t="n">
         <v>43.81999969482422</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>41.51263427734375</v>
+        <v>41.51263046264648</v>
       </c>
       <c r="C235" t="n">
         <v>43.41999816894531</v>
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>42.13308334350586</v>
+        <v>42.13308715820312</v>
       </c>
       <c r="C237" t="n">
         <v>43.68000030517578</v>
@@ -6830,7 +6842,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,11 +6929,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>42.41341018676758</v>
+        <v>42.41340637207031</v>
       </c>
       <c r="C241" t="n">
         <v>43.59000015258789</v>
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,11 +6987,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>48.13469314575195</v>
+        <v>48.13469696044922</v>
       </c>
       <c r="C243" t="n">
         <v>49.47000122070312</v>
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,11 +7045,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>45.13179779052734</v>
+        <v>45.13179397583008</v>
       </c>
       <c r="C245" t="n">
         <v>45.9900016784668</v>
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>40.68999862670898</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="C250" t="n">
-        <v>40.68999862670898</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="D250" t="n">
-        <v>124240300</v>
+        <v>132337300</v>
       </c>
       <c r="E250" t="n">
         <v>2.73</v>
       </c>
       <c r="F250" t="n">
-        <v>14.9047614017249</v>
+        <v>14.72527500473973</v>
       </c>
       <c r="G250" t="n">
         <v>1023208142</v>
       </c>
       <c r="H250" t="n">
-        <v>41634337892.81745</v>
+        <v>41132968089.04586</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1214223137016437</v>
+        <v>0.1293356596452885</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7498,7 +7510,7 @@
       <c r="I6" t="n">
         <v>2.917261055634808</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K6" t="n">
@@ -7511,13 +7523,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7544,7 +7556,7 @@
       <c r="I7" t="n">
         <v>2.952924393723253</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K7" t="n">
@@ -7557,13 +7569,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40381</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7590,7 +7602,7 @@
       <c r="I8" t="n">
         <v>2.724679029957204</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K8" t="n">
@@ -7603,13 +7615,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7636,7 +7648,7 @@
       <c r="I9" t="n">
         <v>2.817403708987161</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K9" t="n">
@@ -7649,13 +7661,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7682,7 +7694,7 @@
       <c r="I10" t="n">
         <v>2.75320970042796</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K10" t="n">
@@ -7695,13 +7707,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40542</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7728,7 +7740,7 @@
       <c r="I11" t="n">
         <v>2.667617689015692</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K11" t="n">
@@ -7741,13 +7753,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7774,7 +7786,7 @@
       <c r="I12" t="n">
         <v>2.853067047075607</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K12" t="n">
@@ -7787,13 +7799,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7820,7 +7832,7 @@
       <c r="I13" t="n">
         <v>2.589158345221113</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K13" t="n">
@@ -7833,13 +7845,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7866,7 +7878,7 @@
       <c r="I14" t="n">
         <v>2.674750356633381</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="K14" t="n">
@@ -7879,13 +7891,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7912,7 +7924,7 @@
       <c r="I15" t="n">
         <v>2.154065620542083</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="K15" t="n">
@@ -7925,13 +7937,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="I16" t="n">
         <v>1.726105563480742</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="K16" t="n">
@@ -7971,13 +7983,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8004,7 +8016,7 @@
       <c r="I17" t="n">
         <v>1.333808844507846</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K17" t="n">
@@ -8017,13 +8029,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8050,7 +8062,7 @@
       <c r="I18" t="n">
         <v>0.9985734664764623</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K18" t="n">
@@ -8063,13 +8075,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8096,7 +8108,7 @@
       <c r="I19" t="n">
         <v>0.7917261055634808</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="K19" t="n">
@@ -8109,13 +8121,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8142,7 +8154,7 @@
       <c r="I20" t="n">
         <v>0.9629101283880172</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K20" t="n">
@@ -8155,13 +8167,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8188,7 +8200,7 @@
       <c r="I21" t="n">
         <v>1.326676176890157</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K21" t="n">
@@ -8201,13 +8213,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8234,7 +8246,7 @@
       <c r="I22" t="n">
         <v>1.433666191155492</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K22" t="n">
@@ -8247,13 +8259,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8280,7 +8292,7 @@
       <c r="I23" t="n">
         <v>1.512125534950071</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K23" t="n">
@@ -8293,13 +8305,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8326,7 +8338,7 @@
       <c r="I24" t="n">
         <v>1.533523537803138</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K24" t="n">
@@ -8339,13 +8351,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8372,7 +8384,7 @@
       <c r="I25" t="n">
         <v>1.74037089871612</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K25" t="n">
@@ -8385,13 +8397,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8418,7 +8430,7 @@
       <c r="I26" t="n">
         <v>1.333808844507846</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K26" t="n">
@@ -8431,13 +8443,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8464,7 +8476,7 @@
       <c r="I27" t="n">
         <v>1.833095577746077</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K27" t="n">
@@ -8477,13 +8489,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8510,7 +8522,7 @@
       <c r="I28" t="n">
         <v>1.932952924393723</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K28" t="n">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8556,7 +8568,7 @@
       <c r="I29" t="n">
         <v>1.604850213980029</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8569,13 +8581,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8602,7 +8614,7 @@
       <c r="I30" t="n">
         <v>1.825962910128388</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K30" t="n">
@@ -8615,13 +8627,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8648,7 +8660,7 @@
       <c r="I31" t="n">
         <v>1.390870185449358</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K31" t="n">
@@ -8661,13 +8673,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8694,7 +8706,7 @@
       <c r="I32" t="n">
         <v>1.069900142653352</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="K32" t="n">
@@ -8707,13 +8719,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8740,7 +8752,7 @@
       <c r="I33" t="n">
         <v>0.9557774607703282</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K33" t="n">
@@ -8753,13 +8765,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42779</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8786,7 +8798,7 @@
       <c r="I34" t="n">
         <v>0.877318116975749</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42779</v>
       </c>
       <c r="K34" t="n">
@@ -8799,13 +8811,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8832,7 +8844,7 @@
       <c r="I35" t="n">
         <v>1.504992867332382</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8845,13 +8857,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8878,7 +8890,7 @@
       <c r="I36" t="n">
         <v>1.362339514978602</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8891,13 +8903,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8924,7 +8936,7 @@
       <c r="I37" t="n">
         <v>1.590584878744651</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K37" t="n">
@@ -8937,13 +8949,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8970,7 +8982,7 @@
       <c r="I38" t="n">
         <v>2.810271041369472</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K38" t="n">
@@ -8983,13 +8995,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9016,7 +9028,7 @@
       <c r="I39" t="n">
         <v>2.475035663338088</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K39" t="n">
@@ -9029,13 +9041,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9062,7 +9074,7 @@
       <c r="I40" t="n">
         <v>2.810271041369472</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -9075,13 +9087,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9108,7 +9120,7 @@
       <c r="I41" t="n">
         <v>2.746077032810271</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K41" t="n">
@@ -9121,13 +9133,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9154,7 +9166,7 @@
       <c r="I42" t="n">
         <v>1.483594864479315</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="K42" t="n">
@@ -9167,13 +9179,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9200,7 +9212,7 @@
       <c r="I43" t="n">
         <v>1.718972895863053</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K43" t="n">
@@ -9213,13 +9225,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9246,7 +9258,7 @@
       <c r="I44" t="n">
         <v>1.676176890156919</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9259,13 +9271,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9292,7 +9304,7 @@
       <c r="I45" t="n">
         <v>1.697574893009986</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K45" t="n">
@@ -9305,13 +9317,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9338,7 +9350,7 @@
       <c r="I46" t="n">
         <v>2.146932952924394</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="K46" t="n">
@@ -9351,13 +9363,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9384,7 +9396,7 @@
       <c r="I47" t="n">
         <v>1.911554921540656</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K47" t="n">
@@ -9397,13 +9409,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9430,7 +9442,7 @@
       <c r="I48" t="n">
         <v>1.932952924393724</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -9443,13 +9455,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9476,7 +9488,7 @@
       <c r="I49" t="n">
         <v>1.733238231098431</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K49" t="n">
@@ -9489,13 +9501,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9522,7 +9534,7 @@
       <c r="I50" t="n">
         <v>1.433666191155492</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K50" t="n">
@@ -9535,13 +9547,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9568,7 +9580,7 @@
       <c r="I51" t="n">
         <v>0.7917261055634806</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K51" t="n">
@@ -9581,13 +9593,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9614,7 +9626,7 @@
       <c r="I52" t="n">
         <v>0.7061340941512122</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K52" t="n">
@@ -9627,13 +9639,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9660,7 +9672,7 @@
       <c r="I53" t="n">
         <v>1.219686162624821</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K53" t="n">
@@ -9673,13 +9685,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9706,7 +9718,7 @@
       <c r="I54" t="n">
         <v>1.74</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K54" t="n">
@@ -9719,13 +9731,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9752,7 +9764,7 @@
       <c r="I55" t="n">
         <v>2.562542719662169</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="K55" t="n">
@@ -9765,13 +9777,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9798,7 +9810,7 @@
       <c r="I56" t="n">
         <v>2.743626768925514</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K56" t="n">
@@ -9811,13 +9823,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9844,7 +9856,7 @@
       <c r="I57" t="n">
         <v>2.549827357713162</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K57" t="n">
@@ -9857,13 +9869,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9890,7 +9902,7 @@
       <c r="I58" t="n">
         <v>2.203294788088354</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K58" t="n">
@@ -9903,13 +9915,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9936,7 +9948,7 @@
       <c r="I59" t="n">
         <v>2.266418843944807</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K59" t="n">
@@ -9949,13 +9961,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9982,7 +9994,7 @@
       <c r="I60" t="n">
         <v>2.137272932396373</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K60" t="n">
@@ -9995,13 +10007,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10028,7 +10040,7 @@
       <c r="I61" t="n">
         <v>2.155860545589846</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K61" t="n">
@@ -10041,13 +10053,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10074,7 +10086,7 @@
       <c r="I62" t="n">
         <v>2.336024136667029</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K62" t="n">
@@ -10087,13 +10099,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10120,7 +10132,7 @@
       <c r="I63" t="n">
         <v>2.324337389679077</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10133,13 +10145,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10166,7 +10178,7 @@
       <c r="I64" t="n">
         <v>2.429959879638917</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -10179,13 +10191,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10212,7 +10224,7 @@
       <c r="I65" t="n">
         <v>2.427853560682046</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K65" t="n">
@@ -10225,13 +10237,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10258,7 +10270,7 @@
       <c r="I66" t="n">
         <v>2.45</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K66" t="n">
@@ -10271,13 +10283,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10304,7 +10316,7 @@
       <c r="I67" t="n">
         <v>2.69</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K67" t="n">
@@ -10317,13 +10329,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10350,7 +10362,7 @@
       <c r="I68" t="n">
         <v>2.63</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K68" t="n">
@@ -10363,13 +10375,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10396,7 +10408,7 @@
       <c r="I69" t="n">
         <v>2.79</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K69" t="n">
@@ -10409,13 +10421,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10442,7 +10454,7 @@
       <c r="I70" t="n">
         <v>2.73</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K70" t="n">
@@ -10455,13 +10467,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10488,7 +10500,7 @@
       <c r="I71" t="n">
         <v>2.73</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K71" t="n">
@@ -10501,13 +10513,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10528,7 +10540,7 @@
       <c r="I72" t="n">
         <v>2.73</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10565,52 +10577,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="C2" t="n">
@@ -10639,10 +10651,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="C3" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40214</v>
       </c>
       <c r="C4" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40381</v>
       </c>
       <c r="C5" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="C6" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="C7" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C8" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C9" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C10" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="C11" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="C12" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="C13" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C14" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C15" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="C16" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C17" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C18" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C19" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C20" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C21" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C22" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C23" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C24" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C25" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C26" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C27" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C28" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="C29" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C30" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42779</v>
       </c>
       <c r="C31" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C32" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C33" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C34" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C35" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C36" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C37" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C38" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="C39" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C40" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C41" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C42" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="C43" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C44" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C45" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C46" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C47" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C48" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C49" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C50" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C51" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="C52" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C53" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C54" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C55" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C56" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C57" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C58" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C59" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C61" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C62" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C63" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C64" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C65" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C66" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C67" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C68" t="n">
@@ -12769,12 +12781,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12845,7 +12857,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/EXC.xlsx
+++ b/salidas/empresas/EXC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>18.74026298522949</v>
+        <v>18.74026870727539</v>
       </c>
       <c r="C2" t="n">
         <v>40.95577621459961</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.7721004486084</v>
+        <v>18.7721061706543</v>
       </c>
       <c r="C3" t="n">
         <v>40.73466491699219</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.38826751708984</v>
+        <v>17.38826942443848</v>
       </c>
       <c r="C4" t="n">
         <v>37.7318115234375</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>17.74984931945801</v>
+        <v>17.74984550476074</v>
       </c>
       <c r="C5" t="n">
         <v>38.51640319824219</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.7432804107666</v>
+        <v>18.74327659606934</v>
       </c>
       <c r="C6" t="n">
         <v>40.37803268432617</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.32993698120117</v>
+        <v>20.32993316650391</v>
       </c>
       <c r="C9" t="n">
         <v>43.4950065612793</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.18324279785156</v>
+        <v>20.1832447052002</v>
       </c>
       <c r="C10" t="n">
         <v>43.18117141723633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.6633243560791</v>
+        <v>20.6633186340332</v>
       </c>
       <c r="C11" t="n">
         <v>44.20827484130859</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.38236618041992</v>
+        <v>20.38235473632812</v>
       </c>
       <c r="C12" t="n">
         <v>43.31668853759766</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.77167320251465</v>
+        <v>20.77168273925781</v>
       </c>
       <c r="C13" t="n">
         <v>44.14408111572266</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.13400077819824</v>
+        <v>20.13398742675781</v>
       </c>
       <c r="C14" t="n">
         <v>42.78887176513672</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.28147315979004</v>
+        <v>22.2814826965332</v>
       </c>
       <c r="C15" t="n">
         <v>47.02567672729492</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.22099494934082</v>
+        <v>23.22100448608398</v>
       </c>
       <c r="C16" t="n">
         <v>49.00856018066406</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>25.48530578613281</v>
+        <v>25.48530006408691</v>
       </c>
       <c r="C17" t="n">
         <v>53.78744888305664</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.67789840698242</v>
+        <v>24.67790603637695</v>
       </c>
       <c r="C19" t="n">
         <v>51.78316879272461</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>23.84511184692383</v>
+        <v>23.8451099395752</v>
       </c>
       <c r="C20" t="n">
         <v>50.03566360473633</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.1678409576416</v>
+        <v>24.1678295135498</v>
       </c>
       <c r="C21" t="n">
         <v>50.40656280517578</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.77172470092773</v>
+        <v>25.7717342376709</v>
       </c>
       <c r="C22" t="n">
         <v>53.75178146362305</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.30922698974609</v>
+        <v>28.30923843383789</v>
       </c>
       <c r="C23" t="n">
         <v>59.04422378540039</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>27.87942123413086</v>
+        <v>27.87941551208496</v>
       </c>
       <c r="C24" t="n">
         <v>57.82453536987305</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.0754337310791</v>
+        <v>28.075439453125</v>
       </c>
       <c r="C25" t="n">
         <v>58.23109817504883</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>26.17026519775391</v>
+        <v>26.17026710510254</v>
       </c>
       <c r="C26" t="n">
         <v>54.27960205078125</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>25.90308380126953</v>
+        <v>25.9030933380127</v>
       </c>
       <c r="C27" t="n">
         <v>53.38801574707031</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>28.12485885620117</v>
+        <v>28.12484359741211</v>
       </c>
       <c r="C28" t="n">
         <v>57.96718978881836</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>29.581787109375</v>
+        <v>29.58177947998047</v>
       </c>
       <c r="C29" t="n">
         <v>60.97004318237305</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>30.63567733764648</v>
+        <v>30.63569259643555</v>
       </c>
       <c r="C30" t="n">
         <v>62.76747512817383</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>31.31803894042969</v>
+        <v>31.31802558898926</v>
       </c>
       <c r="C31" t="n">
         <v>64.16548156738281</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.37019920349121</v>
+        <v>27.37019729614258</v>
       </c>
       <c r="C32" t="n">
         <v>56.07703399658203</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.62383842468262</v>
+        <v>26.62384414672852</v>
       </c>
       <c r="C33" t="n">
         <v>54.17974472045898</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.94820213317871</v>
+        <v>21.94819068908691</v>
       </c>
       <c r="C34" t="n">
         <v>44.66476440429688</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.01101493835449</v>
+        <v>19.01102256774902</v>
       </c>
       <c r="C35" t="n">
         <v>38.68758773803711</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.90054130554199</v>
+        <v>19.90053939819336</v>
       </c>
       <c r="C36" t="n">
         <v>40.09272384643555</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.68811988830566</v>
+        <v>19.68812942504883</v>
       </c>
       <c r="C37" t="n">
         <v>39.66476440429688</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.19600677490234</v>
+        <v>19.19600296020508</v>
       </c>
       <c r="C38" t="n">
         <v>38.67332458496094</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>16.87594413757324</v>
+        <v>16.87593841552734</v>
       </c>
       <c r="C39" t="n">
         <v>33.68045425415039</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>16.22192001342773</v>
+        <v>16.22191619873047</v>
       </c>
       <c r="C40" t="n">
         <v>32.37517929077148</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.4916820526123</v>
+        <v>18.49168395996094</v>
       </c>
       <c r="C43" t="n">
         <v>36.52639007568359</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.36530494689941</v>
+        <v>18.36530685424805</v>
       </c>
       <c r="C44" t="n">
         <v>36.27674865722656</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.25207901000977</v>
+        <v>18.2520694732666</v>
       </c>
       <c r="C45" t="n">
         <v>35.67760467529297</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.10611724853516</v>
+        <v>18.10610961914062</v>
       </c>
       <c r="C46" t="n">
         <v>35.39229583740234</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>17.1354923248291</v>
+        <v>17.13549041748047</v>
       </c>
       <c r="C47" t="n">
         <v>33.4950065612793</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.77706527709961</v>
+        <v>17.77706718444824</v>
       </c>
       <c r="C48" t="n">
         <v>34.36519241333008</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>18.03166198730469</v>
+        <v>18.03165817260742</v>
       </c>
       <c r="C49" t="n">
         <v>34.85734558105469</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.1680965423584</v>
+        <v>16.16808700561523</v>
       </c>
       <c r="C51" t="n">
         <v>30.88445091247559</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.35852813720703</v>
+        <v>16.3585262298584</v>
       </c>
       <c r="C52" t="n">
         <v>31.24821662902832</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.27638244628906</v>
+        <v>16.2763671875</v>
       </c>
       <c r="C53" t="n">
         <v>31.0912971496582</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.59262371063232</v>
+        <v>14.59262943267822</v>
       </c>
       <c r="C54" t="n">
         <v>27.53209686279297</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.35445404052734</v>
+        <v>14.35445308685303</v>
       </c>
       <c r="C55" t="n">
         <v>27.08273887634277</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.81371402740479</v>
+        <v>15.81371784210205</v>
       </c>
       <c r="C56" t="n">
         <v>29.8359489440918</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>15.5889949798584</v>
+        <v>15.58899688720703</v>
       </c>
       <c r="C57" t="n">
         <v>29.04422378540039</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.30106353759766</v>
+        <v>16.30107116699219</v>
       </c>
       <c r="C58" t="n">
         <v>30.37089920043945</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.62727737426758</v>
+        <v>15.62727546691895</v>
       </c>
       <c r="C59" t="n">
         <v>29.11554908752441</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>15.26505279541016</v>
+        <v>15.26504898071289</v>
       </c>
       <c r="C60" t="n">
         <v>28.08131217956543</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.4825267791748</v>
+        <v>16.48253631591797</v>
       </c>
       <c r="C62" t="n">
         <v>30.32097053527832</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.18649673461914</v>
+        <v>16.18649482727051</v>
       </c>
       <c r="C64" t="n">
         <v>29.41512107849121</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>16.55152320861816</v>
+        <v>16.5515193939209</v>
       </c>
       <c r="C65" t="n">
         <v>30.07845878601074</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.63339424133301</v>
+        <v>16.63340377807617</v>
       </c>
       <c r="C66" t="n">
         <v>29.8502140045166</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.02687072753906</v>
+        <v>17.02687644958496</v>
       </c>
       <c r="C67" t="n">
         <v>30.55634880065918</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>17.51574516296387</v>
+        <v>17.5157413482666</v>
       </c>
       <c r="C68" t="n">
         <v>31.43366622924805</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.36420249938965</v>
+        <v>17.36419677734375</v>
       </c>
       <c r="C69" t="n">
         <v>30.75606346130371</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>17.8756217956543</v>
+        <v>17.87562942504883</v>
       </c>
       <c r="C71" t="n">
         <v>31.66191291809082</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.05413246154785</v>
+        <v>18.05413436889648</v>
       </c>
       <c r="C72" t="n">
         <v>31.60485076904297</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.6711311340332</v>
+        <v>17.67112922668457</v>
       </c>
       <c r="C73" t="n">
         <v>30.93437957763672</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.13167190551758</v>
+        <v>16.13167381286621</v>
       </c>
       <c r="C75" t="n">
         <v>27.86733245849609</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.24906730651855</v>
+        <v>16.24906921386719</v>
       </c>
       <c r="C76" t="n">
         <v>27.96718978881836</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>16.16617965698242</v>
+        <v>16.16618728637695</v>
       </c>
       <c r="C77" t="n">
         <v>27.82453536987305</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>15.47555160522461</v>
+        <v>15.47555351257324</v>
       </c>
       <c r="C78" t="n">
         <v>26.3766040802002</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.74338531494141</v>
+        <v>15.74338436126709</v>
       </c>
       <c r="C79" t="n">
         <v>26.83309555053711</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.37111282348633</v>
+        <v>16.3711109161377</v>
       </c>
       <c r="C80" t="n">
         <v>27.90299606323242</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>15.47081565856934</v>
+        <v>15.47081756591797</v>
       </c>
       <c r="C81" t="n">
         <v>26.01283836364746</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>15.0932731628418</v>
+        <v>15.09327507019043</v>
       </c>
       <c r="C82" t="n">
         <v>25.37803077697754</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.17811012268066</v>
+        <v>15.17811107635498</v>
       </c>
       <c r="C83" t="n">
         <v>25.52068519592285</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>12.83489322662354</v>
+        <v>12.83489513397217</v>
       </c>
       <c r="C85" t="n">
         <v>21.21255302429199</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.56856250762939</v>
+        <v>13.56856155395508</v>
       </c>
       <c r="C86" t="n">
         <v>22.42510604858398</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.60038089752197</v>
+        <v>13.60038185119629</v>
       </c>
       <c r="C87" t="n">
         <v>22.1041374206543</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.13202381134033</v>
+        <v>15.13201904296875</v>
       </c>
       <c r="C88" t="n">
         <v>24.59343719482422</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>16.4617805480957</v>
+        <v>16.46176528930664</v>
       </c>
       <c r="C89" t="n">
         <v>26.75463676452637</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.87429332733154</v>
+        <v>13.87429809570312</v>
       </c>
       <c r="C90" t="n">
         <v>22.35378074645996</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.54226970672607</v>
+        <v>13.54226589202881</v>
       </c>
       <c r="C92" t="n">
         <v>21.8188304901123</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>13.63407516479492</v>
+        <v>13.6340799331665</v>
       </c>
       <c r="C93" t="n">
         <v>21.74750328063965</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>13.25398540496826</v>
+        <v>13.25398445129395</v>
       </c>
       <c r="C94" t="n">
         <v>21.14122772216797</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>12.7621021270752</v>
+        <v>12.76210689544678</v>
       </c>
       <c r="C95" t="n">
         <v>20.35663223266602</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.16711807250977</v>
+        <v>12.16711711883545</v>
       </c>
       <c r="C96" t="n">
         <v>19.19400978088379</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>12.38414192199707</v>
+        <v>12.38414287567139</v>
       </c>
       <c r="C97" t="n">
         <v>19.536376953125</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>13.11209392547607</v>
+        <v>13.11209106445312</v>
       </c>
       <c r="C98" t="n">
         <v>20.68473625183105</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>13.89577865600586</v>
+        <v>13.89578437805176</v>
       </c>
       <c r="C99" t="n">
         <v>21.6904411315918</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.33517074584961</v>
+        <v>15.33517169952393</v>
       </c>
       <c r="C100" t="n">
         <v>23.93723297119141</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>16.00687980651855</v>
+        <v>16.00688743591309</v>
       </c>
       <c r="C101" t="n">
         <v>24.9857349395752</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>16.97710418701172</v>
+        <v>16.97710227966309</v>
       </c>
       <c r="C102" t="n">
         <v>26.26961517333984</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.81576728820801</v>
+        <v>16.81575965881348</v>
       </c>
       <c r="C103" t="n">
         <v>26.01997184753418</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>14.32658767700195</v>
+        <v>14.3265905380249</v>
       </c>
       <c r="C104" t="n">
         <v>22.16833114624023</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>15.55655002593994</v>
+        <v>15.55654811859131</v>
       </c>
       <c r="C105" t="n">
         <v>23.83737564086914</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>15.86843204498291</v>
+        <v>15.8684253692627</v>
       </c>
       <c r="C106" t="n">
         <v>24.31526374816895</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>17.03214073181152</v>
+        <v>17.03214263916016</v>
       </c>
       <c r="C107" t="n">
         <v>26.09843063354492</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>16.9767894744873</v>
+        <v>16.97678756713867</v>
       </c>
       <c r="C108" t="n">
         <v>25.79885864257812</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>17.4039134979248</v>
+        <v>17.40390968322754</v>
       </c>
       <c r="C109" t="n">
         <v>26.44793128967285</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>16.915771484375</v>
+        <v>16.91577911376953</v>
       </c>
       <c r="C110" t="n">
         <v>25.70613479614258</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>16.06299591064453</v>
+        <v>16.06300163269043</v>
       </c>
       <c r="C111" t="n">
         <v>24.19400978088379</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>15.9162015914917</v>
+        <v>15.91620349884033</v>
       </c>
       <c r="C112" t="n">
         <v>23.97289657592773</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>16.16933822631836</v>
+        <v>16.16934776306152</v>
       </c>
       <c r="C114" t="n">
         <v>24.12981414794922</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>15.01746273040771</v>
+        <v>15.01745796203613</v>
       </c>
       <c r="C115" t="n">
         <v>22.41084289550781</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>15.33769226074219</v>
+        <v>15.33769035339355</v>
       </c>
       <c r="C116" t="n">
         <v>22.88872909545898</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>14.84542274475098</v>
+        <v>14.84542083740234</v>
       </c>
       <c r="C117" t="n">
         <v>21.94008636474609</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>14.33384418487549</v>
+        <v>14.33384799957275</v>
       </c>
       <c r="C118" t="n">
         <v>21.18402290344238</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>13.47477912902832</v>
+        <v>13.47477531433105</v>
       </c>
       <c r="C119" t="n">
         <v>19.91440773010254</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>13.32374382019043</v>
+        <v>13.32374668121338</v>
       </c>
       <c r="C120" t="n">
         <v>19.47931480407715</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.54816341400146</v>
+        <v>13.54816246032715</v>
       </c>
       <c r="C121" t="n">
         <v>19.80741882324219</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>14.42633247375488</v>
+        <v>14.42633056640625</v>
       </c>
       <c r="C122" t="n">
         <v>21.0912971496582</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>15.51361560821533</v>
+        <v>15.51361179351807</v>
       </c>
       <c r="C123" t="n">
         <v>22.46076965332031</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>17.66650390625</v>
+        <v>17.66650581359863</v>
       </c>
       <c r="C124" t="n">
         <v>25.57774543762207</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>17.28716087341309</v>
+        <v>17.28716278076172</v>
       </c>
       <c r="C125" t="n">
         <v>25.02853012084961</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>17.0370979309082</v>
+        <v>17.03709411621094</v>
       </c>
       <c r="C126" t="n">
         <v>24.44365119934082</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>18.07613182067871</v>
+        <v>18.07612800598145</v>
       </c>
       <c r="C127" t="n">
         <v>25.93437957763672</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>18.53349685668945</v>
+        <v>18.53350448608398</v>
       </c>
       <c r="C128" t="n">
         <v>26.59058570861816</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>17.05552101135254</v>
+        <v>17.0555248260498</v>
       </c>
       <c r="C129" t="n">
         <v>24.25107002258301</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>16.6993579864502</v>
+        <v>16.69936752319336</v>
       </c>
       <c r="C130" t="n">
         <v>23.74464988708496</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>17.09064102172852</v>
+        <v>17.09063911437988</v>
       </c>
       <c r="C131" t="n">
         <v>24.30099868774414</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>18.77521896362305</v>
+        <v>18.77522468566895</v>
       </c>
       <c r="C135" t="n">
         <v>26.18402290344238</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>18.40187644958496</v>
+        <v>18.40186882019043</v>
       </c>
       <c r="C136" t="n">
         <v>25.66333770751953</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>17.71141242980957</v>
+        <v>17.71141624450684</v>
       </c>
       <c r="C137" t="n">
         <v>24.7004280090332</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>18.75284767150879</v>
+        <v>18.75284385681152</v>
       </c>
       <c r="C138" t="n">
         <v>25.89871597290039</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>18.62889099121094</v>
+        <v>18.6288890838623</v>
       </c>
       <c r="C139" t="n">
         <v>25.72753143310547</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>19.80126190185547</v>
+        <v>19.80126571655273</v>
       </c>
       <c r="C140" t="n">
         <v>27.34664726257324</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>19.73000335693359</v>
+        <v>19.7299976348877</v>
       </c>
       <c r="C141" t="n">
         <v>27.01141166687012</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>19.62580299377441</v>
+        <v>19.62580108642578</v>
       </c>
       <c r="C142" t="n">
         <v>26.86875915527344</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>20.94912338256836</v>
+        <v>20.94912528991699</v>
       </c>
       <c r="C143" t="n">
         <v>28.68045616149902</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>21.90128898620605</v>
+        <v>21.90129089355469</v>
       </c>
       <c r="C144" t="n">
         <v>29.75035667419434</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>20.69359588623047</v>
+        <v>20.69358444213867</v>
       </c>
       <c r="C145" t="n">
         <v>28.10984230041504</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>20.22101783752441</v>
+        <v>20.22101593017578</v>
       </c>
       <c r="C146" t="n">
         <v>27.46790313720703</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>19.63215255737305</v>
+        <v>19.63215446472168</v>
       </c>
       <c r="C147" t="n">
         <v>26.41940116882324</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>21.03141212463379</v>
+        <v>21.03141593933105</v>
       </c>
       <c r="C149" t="n">
         <v>28.30242538452148</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>22.12558937072754</v>
+        <v>22.12558746337891</v>
       </c>
       <c r="C150" t="n">
         <v>29.5221118927002</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>22.77241325378418</v>
+        <v>22.77240753173828</v>
       </c>
       <c r="C151" t="n">
         <v>30.38516426086426</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>22.71895790100098</v>
+        <v>22.71895599365234</v>
       </c>
       <c r="C152" t="n">
         <v>30.3138370513916</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>23.55339241027832</v>
+        <v>23.55339622497559</v>
       </c>
       <c r="C153" t="n">
         <v>31.17688941955566</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>23.52645874023438</v>
+        <v>23.52645683288574</v>
       </c>
       <c r="C154" t="n">
         <v>31.14122772216797</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>23.60727882385254</v>
+        <v>23.6072826385498</v>
       </c>
       <c r="C155" t="n">
         <v>31.24821662902832</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>25.18680191040039</v>
+        <v>25.18679809570312</v>
       </c>
       <c r="C156" t="n">
         <v>33.08844375610352</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>24.48641777038574</v>
+        <v>24.48641586303711</v>
       </c>
       <c r="C157" t="n">
         <v>32.16833114624023</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>25.93062210083008</v>
+        <v>25.93062591552734</v>
       </c>
       <c r="C158" t="n">
         <v>34.06562042236328</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>27.42365264892578</v>
+        <v>27.42366027832031</v>
       </c>
       <c r="C160" t="n">
         <v>35.75606155395508</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>27.87224197387695</v>
+        <v>27.87223625183105</v>
       </c>
       <c r="C161" t="n">
         <v>36.3409423828125</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>26.49525260925293</v>
+        <v>26.4952564239502</v>
       </c>
       <c r="C162" t="n">
         <v>34.29386520385742</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>26.41810607910156</v>
+        <v>26.41811561584473</v>
       </c>
       <c r="C163" t="n">
         <v>34.19400787353516</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>24.83103179931641</v>
+        <v>24.83103561401367</v>
       </c>
       <c r="C164" t="n">
         <v>32.13980102539062</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>26.25273513793945</v>
+        <v>26.25274276733398</v>
       </c>
       <c r="C165" t="n">
         <v>33.70898818969727</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>25.26950454711914</v>
+        <v>25.26951026916504</v>
       </c>
       <c r="C167" t="n">
         <v>32.44650650024414</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>25.53334045410156</v>
+        <v>25.5333423614502</v>
       </c>
       <c r="C169" t="n">
         <v>32.5178337097168</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>26.65346908569336</v>
+        <v>26.65347290039062</v>
       </c>
       <c r="C170" t="n">
         <v>33.94436645507812</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>24.32933807373047</v>
+        <v>24.3293342590332</v>
       </c>
       <c r="C171" t="n">
         <v>30.74892997741699</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>20.77390098571777</v>
+        <v>20.77390289306641</v>
       </c>
       <c r="C172" t="n">
         <v>26.25535011291504</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>20.92627716064453</v>
+        <v>20.92627906799316</v>
       </c>
       <c r="C173" t="n">
         <v>26.44793128967285</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>20.70266151428223</v>
+        <v>20.70266723632812</v>
       </c>
       <c r="C175" t="n">
         <v>25.88445091247559</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>22.02617454528809</v>
+        <v>22.02617263793945</v>
       </c>
       <c r="C176" t="n">
         <v>27.53923034667969</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>21.26677513122559</v>
+        <v>21.26677322387695</v>
       </c>
       <c r="C177" t="n">
         <v>26.32667541503906</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>20.60416412353516</v>
+        <v>20.60416793823242</v>
       </c>
       <c r="C178" t="n">
         <v>25.50641822814941</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>22.98379325866699</v>
+        <v>22.98378753662109</v>
       </c>
       <c r="C179" t="n">
         <v>28.45221138000488</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>23.87785530090332</v>
+        <v>23.87785720825195</v>
       </c>
       <c r="C180" t="n">
         <v>29.29386520385742</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>24.54646110534668</v>
+        <v>24.54645729064941</v>
       </c>
       <c r="C181" t="n">
         <v>30.11412239074707</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>24.16273498535156</v>
+        <v>24.16274070739746</v>
       </c>
       <c r="C182" t="n">
         <v>29.64336776733398</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>26.38192176818848</v>
+        <v>26.38191604614258</v>
       </c>
       <c r="C185" t="n">
         <v>32.05420684814453</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>26.2452507019043</v>
+        <v>26.24524879455566</v>
       </c>
       <c r="C187" t="n">
         <v>31.60485076904297</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>29.2675838470459</v>
+        <v>29.26759147644043</v>
       </c>
       <c r="C189" t="n">
         <v>34.96433639526367</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>28.86159515380859</v>
+        <v>28.86159706115723</v>
       </c>
       <c r="C190" t="n">
         <v>34.47931671142578</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.75731086730957</v>
+        <v>31.75730323791504</v>
       </c>
       <c r="C191" t="n">
         <v>37.93865966796875</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>31.70464706420898</v>
+        <v>31.70465469360352</v>
       </c>
       <c r="C192" t="n">
         <v>37.61055755615234</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>34.72901153564453</v>
+        <v>34.72900390625</v>
       </c>
       <c r="C193" t="n">
         <v>41.19828796386719</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>34.84325408935547</v>
+        <v>34.8432502746582</v>
       </c>
       <c r="C194" t="n">
         <v>41.33380889892578</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>36.17534255981445</v>
+        <v>36.17533493041992</v>
       </c>
       <c r="C195" t="n">
         <v>42.56000137329102</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>39.76227188110352</v>
+        <v>39.76226425170898</v>
       </c>
       <c r="C197" t="n">
         <v>46.77999877929688</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>39.79825592041016</v>
+        <v>39.79826354980469</v>
       </c>
       <c r="C200" t="n">
         <v>46.4900016784668</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>37.86970901489258</v>
+        <v>37.86970520019531</v>
       </c>
       <c r="C201" t="n">
         <v>43.90999984741211</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>32.30697631835938</v>
+        <v>32.30697250366211</v>
       </c>
       <c r="C202" t="n">
         <v>37.45999908447266</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>37.60826873779297</v>
+        <v>37.60827255249023</v>
       </c>
       <c r="C205" t="n">
         <v>43.22999954223633</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>36.75881195068359</v>
+        <v>36.75880432128906</v>
       </c>
       <c r="C208" t="n">
         <v>41.88999938964844</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>35.090576171875</v>
+        <v>35.09056854248047</v>
       </c>
       <c r="C210" t="n">
         <v>39.65000152587891</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>36.05522918701172</v>
+        <v>36.05523300170898</v>
       </c>
       <c r="C211" t="n">
         <v>40.7400016784668</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>37.04643249511719</v>
+        <v>37.04643630981445</v>
       </c>
       <c r="C212" t="n">
         <v>41.86000061035156</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>35.82489013671875</v>
+        <v>35.82488632202148</v>
       </c>
       <c r="C213" t="n">
         <v>40.11999893188477</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>33.74432754516602</v>
+        <v>33.74433135986328</v>
       </c>
       <c r="C214" t="n">
         <v>37.79000091552734</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>34.77121734619141</v>
+        <v>34.77121353149414</v>
       </c>
       <c r="C215" t="n">
         <v>38.93999862670898</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>34.70928955078125</v>
+        <v>34.70929336547852</v>
       </c>
       <c r="C216" t="n">
         <v>38.5099983215332</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>32.35689163208008</v>
+        <v>32.35688781738281</v>
       </c>
       <c r="C217" t="n">
         <v>35.90000152587891</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>31.37446022033691</v>
+        <v>31.37445831298828</v>
       </c>
       <c r="C218" t="n">
         <v>34.81000137329102</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>34.23405456542969</v>
+        <v>34.23405075073242</v>
       </c>
       <c r="C221" t="n">
         <v>37.58000183105469</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>34.54924011230469</v>
+        <v>34.54924392700195</v>
       </c>
       <c r="C222" t="n">
         <v>37.54999923706055</v>
@@ -6411,7 +6411,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>31.84419059753418</v>
+        <v>31.84418869018555</v>
       </c>
       <c r="C223" t="n">
         <v>34.61000061035156</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>35.40505218505859</v>
+        <v>35.40505599975586</v>
       </c>
       <c r="C225" t="n">
         <v>38.09000015258789</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.69164657592773</v>
+        <v>37.691650390625</v>
       </c>
       <c r="C226" t="n">
         <v>40.54999923706055</v>
@@ -6527,7 +6527,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>36.52975845336914</v>
+        <v>36.52975463867188</v>
       </c>
       <c r="C227" t="n">
         <v>39.29999923706055</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>41.88448715209961</v>
+        <v>41.88448333740234</v>
       </c>
       <c r="C231" t="n">
         <v>44.20000076293945</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>44.44303894042969</v>
+        <v>44.44304275512695</v>
       </c>
       <c r="C233" t="n">
         <v>46.90000152587891</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>42.96586227416992</v>
+        <v>42.96585845947266</v>
       </c>
       <c r="C236" t="n">
         <v>44.93999862670898</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>42.13308715820312</v>
+        <v>42.13308334350586</v>
       </c>
       <c r="C237" t="n">
         <v>43.68000030517578</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>44.48667144775391</v>
+        <v>44.48666763305664</v>
       </c>
       <c r="C239" t="n">
         <v>46.11999893188477</v>
@@ -6933,7 +6933,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>42.41340637207031</v>
+        <v>42.41341018676758</v>
       </c>
       <c r="C241" t="n">
         <v>43.59000015258789</v>
@@ -6991,7 +6991,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>48.13469696044922</v>
+        <v>48.13469314575195</v>
       </c>
       <c r="C243" t="n">
         <v>49.47000122070312</v>
@@ -7049,7 +7049,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>45.13179397583008</v>
+        <v>45.13179779052734</v>
       </c>
       <c r="C245" t="n">
         <v>45.9900016784668</v>
